--- a/Data/EXCEL/Transfer/salemon/202208/2252-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/2252-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5E02A9D-029A-4D76-8E98-9DDF3FC8E185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{728ED378-060E-4E35-B196-3DB91A1FC109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="2252-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
-      <name val="新細明體"/>
-      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,21 +1226,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" customWidth="1"/>
-    <col min="2" max="5" width="9.75" customWidth="1"/>
-    <col min="6" max="6" width="9.25" customWidth="1"/>
-    <col min="7" max="7" width="10.625" customWidth="1"/>
-    <col min="8" max="9" width="9.75" customWidth="1"/>
-    <col min="10" max="10" width="11.125" customWidth="1"/>
-    <col min="11" max="11" width="9.75" customWidth="1"/>
-    <col min="12" max="12" width="11.125" customWidth="1"/>
-    <col min="13" max="14" width="9.75" customWidth="1"/>
-    <col min="15" max="15" width="11.125" customWidth="1"/>
-    <col min="16" max="16" width="9.75" customWidth="1"/>
-    <col min="17" max="17" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="15.125" customWidth="1"/>
+    <col min="11" max="11" width="13.25" customWidth="1"/>
+    <col min="12" max="12" width="15.125" customWidth="1"/>
+    <col min="13" max="14" width="13.25" customWidth="1"/>
+    <col min="15" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="13.25" customWidth="1"/>
+    <col min="17" max="17" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,696 +1393,696 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>49.3</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="C5" s="7">
-        <v>39.700000000000003</v>
+        <v>59.9</v>
       </c>
       <c r="D5" s="7">
-        <v>49.5</v>
+        <v>66.2</v>
       </c>
       <c r="E5" s="7">
-        <v>38.950000000000003</v>
+        <v>37</v>
       </c>
       <c r="F5" s="8">
-        <v>-9.6</v>
+        <v>20.2</v>
       </c>
       <c r="G5" s="8">
-        <v>-19.47</v>
+        <v>50.88</v>
       </c>
       <c r="H5" s="9">
-        <v>0.26100000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="I5" s="10">
-        <v>7.77</v>
-      </c>
-      <c r="J5" s="8">
-        <v>-43.4</v>
+        <v>-50.8</v>
+      </c>
+      <c r="J5" s="10">
+        <v>-65.099999999999994</v>
       </c>
       <c r="K5" s="9">
-        <v>1.99</v>
-      </c>
-      <c r="L5" s="8">
-        <v>-72.2</v>
+        <v>2.12</v>
+      </c>
+      <c r="L5" s="10">
+        <v>-71.8</v>
       </c>
       <c r="M5" s="9">
-        <v>0.26100000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="N5" s="10">
-        <v>7.77</v>
-      </c>
-      <c r="O5" s="8">
-        <v>-43.4</v>
+        <v>-50.8</v>
+      </c>
+      <c r="O5" s="10">
+        <v>-65.099999999999994</v>
       </c>
       <c r="P5" s="9">
-        <v>1.99</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>-72.2</v>
+        <v>2.12</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>-71.8</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>58</v>
+        <v>49.3</v>
       </c>
       <c r="C6" s="7">
-        <v>49.3</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="D6" s="7">
-        <v>60</v>
+        <v>49.5</v>
       </c>
       <c r="E6" s="7">
-        <v>49</v>
-      </c>
-      <c r="F6" s="8">
-        <v>-8.6999999999999993</v>
-      </c>
-      <c r="G6" s="8">
-        <v>-15</v>
+        <v>38.950000000000003</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-9.6</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-19.47</v>
       </c>
       <c r="H6" s="9">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="I6" s="10">
-        <v>54.8</v>
-      </c>
-      <c r="J6" s="8">
-        <v>-69</v>
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="I6" s="8">
+        <v>7.77</v>
+      </c>
+      <c r="J6" s="10">
+        <v>-43.4</v>
       </c>
       <c r="K6" s="9">
-        <v>1.73</v>
-      </c>
-      <c r="L6" s="8">
-        <v>-74.2</v>
+        <v>1.99</v>
+      </c>
+      <c r="L6" s="10">
+        <v>-72.2</v>
       </c>
       <c r="M6" s="9">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="N6" s="10">
-        <v>54.8</v>
-      </c>
-      <c r="O6" s="8">
-        <v>-69</v>
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="N6" s="8">
+        <v>7.77</v>
+      </c>
+      <c r="O6" s="10">
+        <v>-43.4</v>
       </c>
       <c r="P6" s="9">
-        <v>1.73</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>-74.2</v>
+        <v>1.99</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>-72.2</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>64.8</v>
+        <v>58</v>
       </c>
       <c r="C7" s="7">
-        <v>58</v>
+        <v>49.3</v>
       </c>
       <c r="D7" s="7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E7" s="7">
-        <v>53</v>
-      </c>
-      <c r="F7" s="8">
-        <v>-6.8</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-10.49</v>
+        <v>49</v>
+      </c>
+      <c r="F7" s="10">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="G7" s="10">
+        <v>-15</v>
       </c>
       <c r="H7" s="9">
-        <v>0.156</v>
-      </c>
-      <c r="I7" s="10">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="J7" s="8">
-        <v>-80.5</v>
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="I7" s="8">
+        <v>54.8</v>
+      </c>
+      <c r="J7" s="10">
+        <v>-69</v>
       </c>
       <c r="K7" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="L7" s="8">
-        <v>-74.8</v>
+        <v>1.73</v>
+      </c>
+      <c r="L7" s="10">
+        <v>-74.2</v>
       </c>
       <c r="M7" s="9">
-        <v>0.156</v>
-      </c>
-      <c r="N7" s="10">
-        <v>34.799999999999997</v>
-      </c>
-      <c r="O7" s="8">
-        <v>-80.5</v>
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="N7" s="8">
+        <v>54.8</v>
+      </c>
+      <c r="O7" s="10">
+        <v>-69</v>
       </c>
       <c r="P7" s="9">
-        <v>1.49</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>-74.8</v>
+        <v>1.73</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>-74.2</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="C8" s="7">
-        <v>64.8</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7">
-        <v>69.400000000000006</v>
+        <v>70</v>
       </c>
       <c r="E8" s="7">
-        <v>54.9</v>
-      </c>
-      <c r="F8" s="8">
-        <v>-0.8</v>
-      </c>
-      <c r="G8" s="8">
-        <v>-1.22</v>
+        <v>53</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-6.8</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-10.49</v>
       </c>
       <c r="H8" s="9">
-        <v>0.11600000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="I8" s="8">
-        <v>-59</v>
-      </c>
-      <c r="J8" s="8">
-        <v>-89.7</v>
+        <v>34.799999999999997</v>
+      </c>
+      <c r="J8" s="10">
+        <v>-80.5</v>
       </c>
       <c r="K8" s="9">
-        <v>1.33</v>
-      </c>
-      <c r="L8" s="8">
-        <v>-74</v>
+        <v>1.49</v>
+      </c>
+      <c r="L8" s="10">
+        <v>-74.8</v>
       </c>
       <c r="M8" s="9">
-        <v>0.11600000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="N8" s="8">
-        <v>-59</v>
-      </c>
-      <c r="O8" s="8">
-        <v>-89.7</v>
+        <v>34.799999999999997</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-80.5</v>
       </c>
       <c r="P8" s="9">
-        <v>1.33</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>-74</v>
+        <v>1.49</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>-74.8</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>77.3</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="C9" s="7">
-        <v>65.599999999999994</v>
+        <v>64.8</v>
       </c>
       <c r="D9" s="7">
-        <v>77.8</v>
+        <v>69.400000000000006</v>
       </c>
       <c r="E9" s="7">
-        <v>59</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-11.7</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-15.14</v>
+        <v>54.9</v>
+      </c>
+      <c r="F9" s="10">
+        <v>-0.8</v>
+      </c>
+      <c r="G9" s="10">
+        <v>-1.22</v>
       </c>
       <c r="H9" s="9">
-        <v>0.28299999999999997</v>
-      </c>
-      <c r="I9" s="8">
-        <v>-20.2</v>
-      </c>
-      <c r="J9" s="8">
-        <v>-78.3</v>
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="I9" s="10">
+        <v>-59</v>
+      </c>
+      <c r="J9" s="10">
+        <v>-89.7</v>
       </c>
       <c r="K9" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="L9" s="8">
-        <v>-69.5</v>
+        <v>1.33</v>
+      </c>
+      <c r="L9" s="10">
+        <v>-74</v>
       </c>
       <c r="M9" s="9">
-        <v>0.28299999999999997</v>
-      </c>
-      <c r="N9" s="8">
-        <v>-20.2</v>
-      </c>
-      <c r="O9" s="8">
-        <v>-78.3</v>
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="N9" s="10">
+        <v>-59</v>
+      </c>
+      <c r="O9" s="10">
+        <v>-89.7</v>
       </c>
       <c r="P9" s="9">
-        <v>1.22</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>-69.5</v>
+        <v>1.33</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>-74</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>84.7</v>
+        <v>77.3</v>
       </c>
       <c r="C10" s="7">
-        <v>77.3</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D10" s="7">
-        <v>85.8</v>
+        <v>77.8</v>
       </c>
       <c r="E10" s="7">
-        <v>75</v>
-      </c>
-      <c r="F10" s="8">
-        <v>-7.4</v>
-      </c>
-      <c r="G10" s="8">
-        <v>-8.74</v>
+        <v>59</v>
+      </c>
+      <c r="F10" s="10">
+        <v>-11.7</v>
+      </c>
+      <c r="G10" s="10">
+        <v>-15.14</v>
       </c>
       <c r="H10" s="9">
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-38.9</v>
-      </c>
-      <c r="J10" s="8">
-        <v>-67</v>
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="I10" s="10">
+        <v>-20.2</v>
+      </c>
+      <c r="J10" s="10">
+        <v>-78.3</v>
       </c>
       <c r="K10" s="9">
-        <v>0.93400000000000005</v>
-      </c>
-      <c r="L10" s="8">
-        <v>-65.2</v>
+        <v>1.22</v>
+      </c>
+      <c r="L10" s="10">
+        <v>-69.5</v>
       </c>
       <c r="M10" s="9">
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="N10" s="8">
-        <v>-38.9</v>
-      </c>
-      <c r="O10" s="8">
-        <v>-67</v>
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="N10" s="10">
+        <v>-20.2</v>
+      </c>
+      <c r="O10" s="10">
+        <v>-78.3</v>
       </c>
       <c r="P10" s="9">
-        <v>0.93400000000000005</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>-65.2</v>
+        <v>1.22</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>-69.5</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>90</v>
+        <v>84.7</v>
       </c>
       <c r="C11" s="7">
-        <v>84.7</v>
+        <v>77.3</v>
       </c>
       <c r="D11" s="7">
-        <v>92.9</v>
+        <v>85.8</v>
       </c>
       <c r="E11" s="7">
-        <v>82.9</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-5.3</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-5.89</v>
+        <v>75</v>
+      </c>
+      <c r="F11" s="10">
+        <v>-7.4</v>
+      </c>
+      <c r="G11" s="10">
+        <v>-8.74</v>
       </c>
       <c r="H11" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I11" s="8">
-        <v>-7.76</v>
-      </c>
-      <c r="J11" s="8">
-        <v>-64</v>
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="I11" s="10">
+        <v>-38.9</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-67</v>
       </c>
       <c r="K11" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="L11" s="8">
-        <v>-64</v>
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="L11" s="10">
+        <v>-65.2</v>
       </c>
       <c r="M11" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="N11" s="8">
-        <v>-7.76</v>
-      </c>
-      <c r="O11" s="8">
-        <v>-64</v>
+        <v>0.35399999999999998</v>
+      </c>
+      <c r="N11" s="10">
+        <v>-38.9</v>
+      </c>
+      <c r="O11" s="10">
+        <v>-67</v>
       </c>
       <c r="P11" s="9">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>-64</v>
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>-65.2</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>93.9</v>
+        <v>90</v>
       </c>
       <c r="C12" s="7">
-        <v>90</v>
+        <v>84.7</v>
       </c>
       <c r="D12" s="7">
-        <v>94.8</v>
+        <v>92.9</v>
       </c>
       <c r="E12" s="7">
-        <v>89.5</v>
-      </c>
-      <c r="F12" s="8">
-        <v>-3.9</v>
-      </c>
-      <c r="G12" s="8">
-        <v>-4.1500000000000004</v>
+        <v>82.9</v>
+      </c>
+      <c r="F12" s="10">
+        <v>-5.3</v>
+      </c>
+      <c r="G12" s="10">
+        <v>-5.89</v>
       </c>
       <c r="H12" s="9">
-        <v>0.629</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I12" s="10">
-        <v>210.3</v>
-      </c>
-      <c r="J12" s="8">
-        <v>-54.7</v>
+        <v>-7.76</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-64</v>
       </c>
       <c r="K12" s="9">
-        <v>8.94</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L12" s="10">
-        <v>56.4</v>
+        <v>-64</v>
       </c>
       <c r="M12" s="9">
-        <v>0.629</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="N12" s="10">
-        <v>210.3</v>
-      </c>
-      <c r="O12" s="8">
-        <v>-54.7</v>
+        <v>-7.76</v>
+      </c>
+      <c r="O12" s="10">
+        <v>-64</v>
       </c>
       <c r="P12" s="9">
-        <v>8.94</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Q12" s="10">
-        <v>56.4</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>95.3</v>
+        <v>93.9</v>
       </c>
       <c r="C13" s="7">
-        <v>93.9</v>
+        <v>90</v>
       </c>
       <c r="D13" s="7">
-        <v>103</v>
+        <v>94.8</v>
       </c>
       <c r="E13" s="7">
-        <v>89.1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>-1.4</v>
-      </c>
-      <c r="G13" s="8">
-        <v>-1.47</v>
+        <v>89.5</v>
+      </c>
+      <c r="F13" s="10">
+        <v>-3.9</v>
+      </c>
+      <c r="G13" s="10">
+        <v>-4.1500000000000004</v>
       </c>
       <c r="H13" s="9">
-        <v>0.20300000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="I13" s="8">
-        <v>-48.2</v>
-      </c>
-      <c r="J13" s="8">
-        <v>-76.3</v>
+        <v>210.3</v>
+      </c>
+      <c r="J13" s="10">
+        <v>-54.7</v>
       </c>
       <c r="K13" s="9">
-        <v>8.31</v>
-      </c>
-      <c r="L13" s="10">
-        <v>92.1</v>
+        <v>8.94</v>
+      </c>
+      <c r="L13" s="8">
+        <v>56.4</v>
       </c>
       <c r="M13" s="9">
-        <v>0.20300000000000001</v>
+        <v>0.629</v>
       </c>
       <c r="N13" s="8">
-        <v>-48.2</v>
-      </c>
-      <c r="O13" s="8">
-        <v>-76.3</v>
+        <v>210.3</v>
+      </c>
+      <c r="O13" s="10">
+        <v>-54.7</v>
       </c>
       <c r="P13" s="9">
-        <v>8.31</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>92.1</v>
+        <v>8.94</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>56.4</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="C14" s="7">
-        <v>95.3</v>
+        <v>93.9</v>
       </c>
       <c r="D14" s="7">
-        <v>98.8</v>
+        <v>103</v>
       </c>
       <c r="E14" s="7">
-        <v>81.7</v>
+        <v>89.1</v>
       </c>
       <c r="F14" s="10">
-        <v>0.1</v>
+        <v>-1.4</v>
       </c>
       <c r="G14" s="10">
-        <v>0.11</v>
+        <v>-1.47</v>
       </c>
       <c r="H14" s="9">
-        <v>0.39100000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="I14" s="10">
-        <v>101.6</v>
-      </c>
-      <c r="J14" s="8">
-        <v>-58.9</v>
+        <v>-48.2</v>
+      </c>
+      <c r="J14" s="10">
+        <v>-76.3</v>
       </c>
       <c r="K14" s="9">
-        <v>8.11</v>
-      </c>
-      <c r="L14" s="10">
-        <v>133.6</v>
+        <v>8.31</v>
+      </c>
+      <c r="L14" s="8">
+        <v>92.1</v>
       </c>
       <c r="M14" s="9">
-        <v>0.39100000000000001</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="N14" s="10">
-        <v>101.6</v>
-      </c>
-      <c r="O14" s="8">
-        <v>-58.9</v>
+        <v>-48.2</v>
+      </c>
+      <c r="O14" s="10">
+        <v>-76.3</v>
       </c>
       <c r="P14" s="9">
-        <v>8.11</v>
-      </c>
-      <c r="Q14" s="10">
-        <v>133.6</v>
+        <v>8.31</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>92.1</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>115.5</v>
+        <v>95.2</v>
       </c>
       <c r="C15" s="7">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="D15" s="7">
-        <v>126.5</v>
+        <v>98.8</v>
       </c>
       <c r="E15" s="7">
-        <v>92.6</v>
+        <v>81.7</v>
       </c>
       <c r="F15" s="8">
-        <v>-20.3</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="8">
-        <v>-17.579999999999998</v>
+        <v>0.11</v>
       </c>
       <c r="H15" s="9">
-        <v>0.19400000000000001</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="I15" s="8">
-        <v>-47.2</v>
-      </c>
-      <c r="J15" s="8">
-        <v>-78.3</v>
+        <v>101.6</v>
+      </c>
+      <c r="J15" s="10">
+        <v>-58.9</v>
       </c>
       <c r="K15" s="9">
-        <v>7.72</v>
-      </c>
-      <c r="L15" s="10">
-        <v>206.2</v>
+        <v>8.11</v>
+      </c>
+      <c r="L15" s="8">
+        <v>133.6</v>
       </c>
       <c r="M15" s="9">
-        <v>0.19400000000000001</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="N15" s="8">
-        <v>-47.2</v>
-      </c>
-      <c r="O15" s="8">
-        <v>-78.3</v>
+        <v>101.6</v>
+      </c>
+      <c r="O15" s="10">
+        <v>-58.9</v>
       </c>
       <c r="P15" s="9">
-        <v>7.72</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>206.2</v>
+        <v>8.11</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>133.6</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>93.1</v>
+        <v>115.5</v>
       </c>
       <c r="C16" s="7">
-        <v>115.5</v>
+        <v>95.2</v>
       </c>
       <c r="D16" s="7">
-        <v>125.5</v>
+        <v>126.5</v>
       </c>
       <c r="E16" s="7">
-        <v>80</v>
+        <v>92.6</v>
       </c>
       <c r="F16" s="10">
-        <v>22.4</v>
+        <v>-20.3</v>
       </c>
       <c r="G16" s="10">
-        <v>24.06</v>
+        <v>-17.579999999999998</v>
       </c>
       <c r="H16" s="9">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="I16" s="8">
-        <v>-20.2</v>
-      </c>
-      <c r="J16" s="8">
-        <v>-57.5</v>
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="I16" s="10">
+        <v>-47.2</v>
+      </c>
+      <c r="J16" s="10">
+        <v>-78.3</v>
       </c>
       <c r="K16" s="9">
-        <v>7.53</v>
-      </c>
-      <c r="L16" s="10">
-        <v>362.7</v>
+        <v>7.72</v>
+      </c>
+      <c r="L16" s="8">
+        <v>206.2</v>
       </c>
       <c r="M16" s="9">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="N16" s="8">
-        <v>-20.2</v>
-      </c>
-      <c r="O16" s="8">
-        <v>-57.5</v>
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="N16" s="10">
+        <v>-47.2</v>
+      </c>
+      <c r="O16" s="10">
+        <v>-78.3</v>
       </c>
       <c r="P16" s="9">
-        <v>7.53</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>362.7</v>
+        <v>7.72</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>206.2</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>17</v>
+        <v>44409</v>
+      </c>
+      <c r="B17" s="7">
+        <v>93.1</v>
+      </c>
+      <c r="C17" s="7">
+        <v>115.5</v>
+      </c>
+      <c r="D17" s="7">
+        <v>125.5</v>
+      </c>
+      <c r="E17" s="7">
+        <v>80</v>
+      </c>
+      <c r="F17" s="8">
+        <v>22.4</v>
+      </c>
+      <c r="G17" s="8">
+        <v>24.06</v>
       </c>
       <c r="H17" s="9">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="I17" s="8">
-        <v>-41</v>
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="I17" s="10">
+        <v>-20.2</v>
       </c>
       <c r="J17" s="10">
-        <v>62</v>
+        <v>-57.5</v>
       </c>
       <c r="K17" s="9">
-        <v>7.16</v>
-      </c>
-      <c r="L17" s="10">
-        <v>838.6</v>
+        <v>7.53</v>
+      </c>
+      <c r="L17" s="8">
+        <v>362.7</v>
       </c>
       <c r="M17" s="9">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="N17" s="8">
-        <v>-41</v>
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="N17" s="10">
+        <v>-20.2</v>
       </c>
       <c r="O17" s="10">
-        <v>62</v>
+        <v>-57.5</v>
       </c>
       <c r="P17" s="9">
-        <v>7.16</v>
-      </c>
-      <c r="Q17" s="10">
-        <v>838.6</v>
+        <v>7.53</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>362.7</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>17</v>
@@ -2095,39 +2103,39 @@
         <v>17</v>
       </c>
       <c r="H18" s="9">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="I18" s="8">
-        <v>-2.44</v>
-      </c>
-      <c r="J18" s="10">
-        <v>677.5</v>
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="I18" s="10">
+        <v>-41</v>
+      </c>
+      <c r="J18" s="8">
+        <v>62</v>
       </c>
       <c r="K18" s="9">
-        <v>6.7</v>
-      </c>
-      <c r="L18" s="10">
-        <v>1300</v>
+        <v>7.16</v>
+      </c>
+      <c r="L18" s="8">
+        <v>838.6</v>
       </c>
       <c r="M18" s="9">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="N18" s="8">
-        <v>-2.44</v>
-      </c>
-      <c r="O18" s="10">
-        <v>677.5</v>
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="N18" s="10">
+        <v>-41</v>
+      </c>
+      <c r="O18" s="8">
+        <v>62</v>
       </c>
       <c r="P18" s="9">
-        <v>6.7</v>
-      </c>
-      <c r="Q18" s="10">
-        <v>1300</v>
+        <v>7.16</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>838.6</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>17</v>
@@ -2148,33 +2156,86 @@
         <v>17</v>
       </c>
       <c r="H19" s="9">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="I19" s="10">
+        <v>-2.44</v>
+      </c>
+      <c r="J19" s="8">
+        <v>677.5</v>
+      </c>
+      <c r="K19" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1300</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="N19" s="10">
+        <v>-2.44</v>
+      </c>
+      <c r="O19" s="8">
+        <v>677.5</v>
+      </c>
+      <c r="P19" s="9">
+        <v>6.7</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>44317</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="9">
         <v>0.80100000000000005</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J20" s="8">
         <v>1443.4</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K20" s="9">
         <v>5.92</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L20" s="8">
         <v>1465.4</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M20" s="9">
         <v>0.80100000000000005</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="N20" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O20" s="8">
         <v>1443.4</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P20" s="9">
         <v>5.92</v>
       </c>
-      <c r="Q19" s="10">
+      <c r="Q20" s="8">
         <v>1465.4</v>
       </c>
     </row>
@@ -2193,7 +2254,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>